--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\catalog generator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F21C3E4-01FD-4E22-ACEB-83025123B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91C0B17-B162-4F55-B232-0758E9E309A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{49E1CB35-F73E-4962-90A7-0A93768B79B6}"/>
   </bookViews>
